--- a/samples/calibration01/stereo_calib.xlsx
+++ b/samples/calibration01/stereo_calib.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
